--- a/data/trans_dic/P43-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P43-Estudios-trans_dic.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -518,22 +518,18 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han realizado alguna vez una mamografía por prescripción de algún especialista</t>
+          <t>Población a la que le han realizado alguna vez una mamografía por prescripción de algún especialista (tasa de respuesta: 99,33%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,20 +537,12 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -595,26 +583,6 @@
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -631,10 +599,6 @@
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -649,22 +613,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>63,87%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,26 +647,6 @@
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>64,98%</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>47,58%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>63,87%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>65,46%</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>64,98%</t>
         </is>
@@ -717,62 +661,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>44,67; 50,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>60,9; 66,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>62,06; 68,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>61,85; 68,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>44,67; 50,3</t>
+          <t>44,67; 50,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,92; 66,28</t>
+          <t>60,9; 66,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,32; 68,56</t>
+          <t>62,06; 68,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>62,02; 68,18</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>44,67; 50,3</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>60,92; 66,28</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>62,32; 68,56</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>62,02; 68,18</t>
+          <t>61,85; 68,36</t>
         </is>
       </c>
     </row>
@@ -789,22 +713,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,23%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,26 +747,6 @@
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>52,23%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>30,51%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>37,54%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>43,41%</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>52,23%</t>
         </is>
@@ -857,62 +761,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>28,58; 33,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>35,03; 40,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>40,94; 45,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>44,48; 67,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,19; 32,75</t>
+          <t>28,58; 33,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,18; 40,09</t>
+          <t>35,03; 40,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,25; 45,91</t>
+          <t>40,94; 45,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>43,86; 69,15</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>28,19; 32,75</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>35,18; 40,09</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>41,25; 45,91</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>43,86; 69,15</t>
+          <t>44,48; 67,9</t>
         </is>
       </c>
     </row>
@@ -929,22 +813,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>57,95%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,26 +847,6 @@
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>57,95%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>35,9%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>35,02%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>45,3%</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>57,95%</t>
         </is>
@@ -997,62 +861,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>31,93; 40,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>30,39; 40,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>41,02; 49,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>53,83; 62,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>31,54; 40,5</t>
+          <t>31,93; 40,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30,28; 40,53</t>
+          <t>30,39; 40,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>41,08; 50,03</t>
+          <t>41,02; 49,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>53,71; 61,83</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>31,54; 40,5</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>30,28; 40,53</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>41,08; 50,03</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>53,71; 61,83</t>
+          <t>53,83; 62,22</t>
         </is>
       </c>
     </row>
@@ -1069,22 +913,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,93%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,26 +947,6 @@
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>55,93%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>37,91%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>47,14%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>49,89%</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>55,93%</t>
         </is>
@@ -1137,62 +961,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>36,25; 39,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>45,53; 48,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>48,24; 51,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>51,25; 65,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>36,19; 39,57</t>
+          <t>36,25; 39,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,32; 48,8</t>
+          <t>45,53; 48,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,05; 51,53</t>
+          <t>48,24; 51,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>51,14; 66,75</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>36,19; 39,57</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>45,32; 48,8</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>48,05; 51,53</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>51,14; 66,75</t>
+          <t>51,25; 65,83</t>
         </is>
       </c>
     </row>
@@ -1204,15 +1008,14 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="A6:A7"/>
-    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A10:A11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1224,7 +1027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1237,22 +1040,18 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han realizado alguna vez una mamografía por prescripción de algún especialista</t>
+          <t>Población a la que le han realizado alguna vez una mamografía por prescripción de algún especialista (tasa de respuesta: 99,33%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,20 +1059,12 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -1314,26 +1105,6 @@
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -1350,10 +1121,6 @@
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1368,22 +1135,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>625</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>796</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>577</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>792</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1402,26 +1169,6 @@
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>625</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>796</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>577</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>792</t>
         </is>
@@ -1436,22 +1183,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>621366</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>849925</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>644496</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>397625</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1470,26 +1217,6 @@
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>397625</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>621366</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>849925</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>644496</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>397625</t>
         </is>
@@ -1504,62 +1231,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>583427; 656301</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>810387; 883007</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>611076; 675124</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>378477; 418315</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>583360; 656827</t>
+          <t>583427; 656301</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>810559; 881897</t>
+          <t>810387; 883007</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>613636; 675099</t>
+          <t>611076; 675124</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>379482; 417195</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>583360; 656827</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>810559; 881897</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>613636; 675099</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>379482; 417195</t>
+          <t>378477; 418315</t>
         </is>
       </c>
     </row>
@@ -1576,22 +1283,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>465</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>591</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>784</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1198</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1610,26 +1317,6 @@
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1198</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>465</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>784</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1198</t>
         </is>
@@ -1644,22 +1331,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>481836</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>655626</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>857045</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>914307</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1678,26 +1365,6 @@
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>914307</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>481836</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>655626</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>857045</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>914307</t>
         </is>
@@ -1712,62 +1379,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>451438; 522700</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>611629; 699086</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>808402; 901229</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>778691; 1188643</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>445236; 517208</t>
+          <t>451438; 522700</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>614372; 700041</t>
+          <t>611629; 699086</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>814525; 906395</t>
+          <t>808402; 901229</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>767849; 1210561</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>445236; 517208</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>614372; 700041</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>814525; 906395</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>767849; 1210561</t>
+          <t>778691; 1188643</t>
         </is>
       </c>
     </row>
@@ -1784,22 +1431,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>134</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>227</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>471</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1818,26 +1465,6 @@
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>471</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>471</t>
         </is>
@@ -1852,22 +1479,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>170239</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>159533</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>248297</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>267934</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1886,26 +1513,6 @@
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>267934</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>170239</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>159533</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>248297</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>267934</t>
         </is>
@@ -1920,62 +1527,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>151454; 189904</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>138455; 184241</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>224829; 273846</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>248867; 287653</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>149601; 192086</t>
+          <t>151454; 189904</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>137937; 184640</t>
+          <t>138455; 184241</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>225205; 274225</t>
+          <t>224829; 273846</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>248326; 285854</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>149601; 192086</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>137937; 184640</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>225205; 274225</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>248326; 285854</t>
+          <t>248867; 287653</t>
         </is>
       </c>
     </row>
@@ -1992,22 +1579,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2461</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -2026,26 +1613,6 @@
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2461</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1252</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1521</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>1588</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2461</t>
         </is>
@@ -2060,22 +1627,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1273441</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1665084</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1749838</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1579865</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2094,26 +1661,6 @@
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1579865</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1273441</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>1665084</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>1749838</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>1579865</t>
         </is>
@@ -2128,62 +1675,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1217806; 1326804</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1608502; 1727307</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1691886; 1807561</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1447681; 1859675</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1215683; 1329323</t>
+          <t>1217806; 1326804</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1600830; 1723735</t>
+          <t>1608502; 1727307</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1685137; 1807339</t>
+          <t>1691886; 1807561</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1444605; 1885539</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>1215683; 1329323</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>1600830; 1723735</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>1685137; 1807339</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>1444605; 1885539</t>
+          <t>1447681; 1859675</t>
         </is>
       </c>
     </row>
@@ -2195,14 +1722,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A1:B2"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trans_dic/P43-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P43-Estudios-trans_dic.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>64,71%</t>
         </is>
       </c>
     </row>
@@ -661,42 +661,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>44,67; 50,25</t>
+          <t>44,92; 50,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>60,9; 66,36</t>
+          <t>61,05; 66,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>62,06; 68,57</t>
+          <t>61,69; 68,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>61,85; 68,36</t>
+          <t>61,47; 67,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>44,67; 50,25</t>
+          <t>44,92; 50,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,9; 66,36</t>
+          <t>61,05; 66,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,06; 68,57</t>
+          <t>61,69; 68,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>61,85; 68,36</t>
+          <t>61,47; 67,6</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>45,24%</t>
         </is>
       </c>
     </row>
@@ -761,42 +761,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>28,58; 33,1</t>
+          <t>28,21; 32,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>35,03; 40,03</t>
+          <t>35,38; 39,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40,94; 45,64</t>
+          <t>41,3; 45,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44,48; 67,9</t>
+          <t>42,98; 47,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,58; 33,1</t>
+          <t>28,21; 32,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,03; 40,03</t>
+          <t>35,38; 39,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,94; 45,64</t>
+          <t>41,3; 45,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>44,48; 67,9</t>
+          <t>42,98; 47,45</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>58,39%</t>
         </is>
       </c>
     </row>
@@ -861,42 +861,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>31,93; 40,04</t>
+          <t>31,59; 40,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30,39; 40,44</t>
+          <t>30,32; 39,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>41,02; 49,96</t>
+          <t>40,94; 50,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>53,83; 62,22</t>
+          <t>54,31; 62,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>31,93; 40,04</t>
+          <t>31,59; 40,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30,39; 40,44</t>
+          <t>30,32; 39,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>41,02; 49,96</t>
+          <t>40,94; 50,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>53,83; 62,22</t>
+          <t>54,31; 62,35</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>52,28%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>52,28%</t>
         </is>
       </c>
     </row>
@@ -961,42 +961,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>36,25; 39,49</t>
+          <t>36,16; 39,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>45,53; 48,9</t>
+          <t>45,28; 48,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>48,24; 51,54</t>
+          <t>48,19; 51,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51,25; 65,83</t>
+          <t>50,64; 53,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>36,25; 39,49</t>
+          <t>36,16; 39,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,53; 48,9</t>
+          <t>45,28; 48,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,24; 51,54</t>
+          <t>48,19; 51,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>51,25; 65,83</t>
+          <t>50,64; 53,84</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>397625</t>
+          <t>430986</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>397625</t>
+          <t>430986</t>
         </is>
       </c>
     </row>
@@ -1231,42 +1231,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>583427; 656301</t>
+          <t>586579; 657514</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>810387; 883007</t>
+          <t>812285; 887018</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>611076; 675124</t>
+          <t>607365; 670793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>378477; 418315</t>
+          <t>409412; 450254</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>583427; 656301</t>
+          <t>586579; 657514</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>810387; 883007</t>
+          <t>812285; 887018</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>611076; 675124</t>
+          <t>607365; 670793</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>378477; 418315</t>
+          <t>409412; 450254</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>914307</t>
+          <t>732910</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>914307</t>
+          <t>732910</t>
         </is>
       </c>
     </row>
@@ -1379,42 +1379,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>451438; 522700</t>
+          <t>445471; 514822</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>611629; 699086</t>
+          <t>617809; 695045</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>808402; 901229</t>
+          <t>815521; 904625</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>778691; 1188643</t>
+          <t>696334; 768639</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>451438; 522700</t>
+          <t>445471; 514822</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>611629; 699086</t>
+          <t>617809; 695045</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>808402; 901229</t>
+          <t>815521; 904625</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>778691; 1188643</t>
+          <t>696334; 768639</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>267934</t>
+          <t>299107</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>267934</t>
+          <t>299107</t>
         </is>
       </c>
     </row>
@@ -1527,42 +1527,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>151454; 189904</t>
+          <t>149839; 190436</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>138455; 184241</t>
+          <t>138137; 180128</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>224829; 273846</t>
+          <t>224434; 274169</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>248867; 287653</t>
+          <t>278173; 319376</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>151454; 189904</t>
+          <t>149839; 190436</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>138455; 184241</t>
+          <t>138137; 180128</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>224829; 273846</t>
+          <t>224434; 274169</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>248867; 287653</t>
+          <t>278173; 319376</t>
         </is>
       </c>
     </row>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1579865</t>
+          <t>1463003</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1579865</t>
+          <t>1463003</t>
         </is>
       </c>
     </row>
@@ -1675,42 +1675,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1217806; 1326804</t>
+          <t>1214792; 1330182</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1608502; 1727307</t>
+          <t>1599576; 1727552</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1691886; 1807561</t>
+          <t>1690301; 1815252</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1447681; 1859675</t>
+          <t>1416926; 1506547</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1217806; 1326804</t>
+          <t>1214792; 1330182</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1608502; 1727307</t>
+          <t>1599576; 1727552</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1691886; 1807561</t>
+          <t>1690301; 1815252</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1447681; 1859675</t>
+          <t>1416926; 1506547</t>
         </is>
       </c>
     </row>
